--- a/artfynd/A 59140-2025 artfynd.xlsx
+++ b/artfynd/A 59140-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -819,9 +819,134 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>136895488</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57186</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Nygård NO, Skultuna sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>577185</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6622244</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Skultuna</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Anette och Rune Berglinn</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Anette och Rune Berglinn</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136895488</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59140-2025 artfynd.xlsx
+++ b/artfynd/A 59140-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -821,10 +821,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136895488</v>
+        <v>137021038</v>
       </c>
       <c r="B3" t="n">
-        <v>57186</v>
+        <v>57195</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,34 +832,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -898,22 +898,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -938,6 +938,130 @@
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137021038</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136895488</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57186</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Nygård NO, Skultuna sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>577185</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6622244</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Skultuna</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anette och Rune Berglinn</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anette och Rune Berglinn</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136895488</t>
         </is>
@@ -947,6 +1071,7 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59140-2025 artfynd.xlsx
+++ b/artfynd/A 59140-2025 artfynd.xlsx
@@ -824,7 +824,7 @@
         <v>137021038</v>
       </c>
       <c r="B3" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>136895488</v>
       </c>
       <c r="B4" t="n">
-        <v>57186</v>
+        <v>57199</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 59140-2025 artfynd.xlsx
+++ b/artfynd/A 59140-2025 artfynd.xlsx
@@ -824,7 +824,7 @@
         <v>137021038</v>
       </c>
       <c r="B3" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>136895488</v>
       </c>
       <c r="B4" t="n">
-        <v>57199</v>
+        <v>57201</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 59140-2025 artfynd.xlsx
+++ b/artfynd/A 59140-2025 artfynd.xlsx
@@ -855,11 +855,7 @@
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -978,11 +974,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>

--- a/artfynd/A 59140-2025 artfynd.xlsx
+++ b/artfynd/A 59140-2025 artfynd.xlsx
@@ -824,7 +824,7 @@
         <v>137021038</v>
       </c>
       <c r="B3" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         <v>136895488</v>
       </c>
       <c r="B4" t="n">
-        <v>57201</v>
+        <v>57211</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 59140-2025 artfynd.xlsx
+++ b/artfynd/A 59140-2025 artfynd.xlsx
@@ -824,7 +824,7 @@
         <v>137021038</v>
       </c>
       <c r="B3" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         <v>136895488</v>
       </c>
       <c r="B4" t="n">
-        <v>57211</v>
+        <v>57212</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 59140-2025 artfynd.xlsx
+++ b/artfynd/A 59140-2025 artfynd.xlsx
@@ -824,7 +824,7 @@
         <v>137021038</v>
       </c>
       <c r="B3" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         <v>136895488</v>
       </c>
       <c r="B4" t="n">
-        <v>57212</v>
+        <v>57215</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
